--- a/Preparation.xlsx
+++ b/Preparation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dell-my.sharepoint.com/personal/subhajit_ghosh_dell_com/Documents/Documents/AWS-CLEAN/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sghos\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{11225857-4E00-4E0C-880C-07284E85D495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B2F9EF-816A-4784-84E9-85965A74B237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>Day 1: Arrays &amp; Strings</t>
   </si>
@@ -147,6 +147,60 @@
   </si>
   <si>
     <t>Lowest Common Ancestor of BST</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/lowest-common-ancestor-of-a-binary-tree/</t>
+  </si>
+  <si>
+    <t>https://www.geeksforgeeks.org/problems/lowest-common-ancestor-in-a-binary-tree</t>
+  </si>
+  <si>
+    <t>Convert Sorted Array to BST</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/convert-sorted-array-to-binary-search-tree/description/</t>
+  </si>
+  <si>
+    <t>https://www.geeksforgeeks.org/problems/array-to-bst4443/1</t>
+  </si>
+  <si>
+    <t>Kth Smallest Element in BST</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/kth-smallest-element-in-a-bst/</t>
+  </si>
+  <si>
+    <t>Day 6: Sorting Algorithms</t>
+  </si>
+  <si>
+    <t>Sort Colors (LeetCode 75)</t>
+  </si>
+  <si>
+    <t>https://www.geeksforgeeks.org/problems/sort-an-array-of-0s-1s-and-2s4231/1</t>
+  </si>
+  <si>
+    <t>Merge sort</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/merge-sorted-array/description/</t>
+  </si>
+  <si>
+    <t>Day 7: Searching &amp; Binary Search</t>
+  </si>
+  <si>
+    <t>Search Insert Position</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/search-insert-position/submissions/2032889421/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/find-peak-element/description/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Find Peak Element </t>
+  </si>
+  <si>
+    <t xml:space="preserve">             </t>
   </si>
 </sst>
 </file>
@@ -294,10 +348,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -563,28 +613,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:J25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A2:J35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.26171875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="31.578125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="87.15625" customWidth="1"/>
-    <col min="4" max="4" width="18.15625" customWidth="1"/>
-    <col min="5" max="5" width="13.83984375" customWidth="1"/>
-    <col min="6" max="6" width="15.68359375" customWidth="1"/>
-    <col min="7" max="7" width="12.41796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.68359375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.26171875" customWidth="1"/>
-    <col min="10" max="10" width="11.26171875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.85546875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="38.28515625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="87.140625" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.28515625" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="14"/>
     </row>
-    <row r="3" spans="1:10" ht="14.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
@@ -610,7 +660,7 @@
         <v>46183</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C4" s="2" t="s">
         <v>3</v>
       </c>
@@ -621,7 +671,7 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="29.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
@@ -641,7 +691,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C6" s="2" t="s">
         <v>6</v>
       </c>
@@ -658,7 +708,7 @@
         <v>46183</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="29.4" x14ac:dyDescent="0.65">
+    <row r="7" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
         <v>7</v>
       </c>
@@ -672,13 +722,13 @@
         <v>46116</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="15" customFormat="1" ht="16.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="14"/>
     </row>
-    <row r="10" spans="1:10" ht="15" x14ac:dyDescent="0.65">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
         <v>10</v>
       </c>
@@ -707,7 +757,7 @@
         <v>46180</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="16.2" x14ac:dyDescent="0.7">
+    <row r="11" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">
         <v>12</v>
       </c>
@@ -736,7 +786,7 @@
         <v>46183</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="29.4" x14ac:dyDescent="0.65">
+    <row r="12" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
         <v>14</v>
       </c>
@@ -765,13 +815,13 @@
         <v>46180</v>
       </c>
     </row>
-    <row r="14" spans="1:10" s="15" customFormat="1" ht="32.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:10" s="15" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>16</v>
       </c>
       <c r="B14" s="14"/>
     </row>
-    <row r="15" spans="1:10" ht="16.2" x14ac:dyDescent="0.7">
+    <row r="15" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
         <v>17</v>
       </c>
@@ -788,7 +838,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="16.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:10" ht="33" x14ac:dyDescent="0.25">
       <c r="B16" s="12" t="s">
         <v>19</v>
       </c>
@@ -802,7 +852,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>21</v>
       </c>
@@ -810,7 +860,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C18" s="2" t="s">
         <v>23</v>
       </c>
@@ -821,13 +871,13 @@
         <v>46183</v>
       </c>
     </row>
-    <row r="19" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>24</v>
       </c>
       <c r="B19" s="14"/>
     </row>
-    <row r="20" spans="1:5" ht="16.2" x14ac:dyDescent="0.7">
+    <row r="20" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B20" s="5" t="s">
         <v>25</v>
       </c>
@@ -841,7 +891,7 @@
         <v>46183</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>27</v>
       </c>
@@ -855,7 +905,7 @@
         <v>46183</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C22" s="2" t="s">
         <v>29</v>
       </c>
@@ -863,7 +913,7 @@
         <v>46183</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="16.2" x14ac:dyDescent="0.7">
+    <row r="23" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B23" s="17" t="s">
         <v>31</v>
       </c>
@@ -873,16 +923,129 @@
       <c r="D23" s="4">
         <v>46183</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="E23" s="10">
+        <v>46188</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>30</v>
       </c>
       <c r="B24" s="14"/>
     </row>
-    <row r="25" spans="1:5" ht="16.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="B25" s="18" t="s">
         <v>33</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="4">
+        <v>46185</v>
+      </c>
+      <c r="E25" s="9">
+        <v>46187</v>
+      </c>
+      <c r="F25" s="9">
+        <v>46188</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C26" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B27" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" s="4">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C28" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D28" s="11">
+        <v>46187</v>
+      </c>
+      <c r="H28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="9">
+        <v>46187</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="14"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" s="11">
+        <v>46187</v>
+      </c>
+      <c r="E31" s="11">
+        <v>46190</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D32" s="9"/>
+    </row>
+    <row r="33" spans="1:5" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" s="14"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B34" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D34" s="9">
+        <v>46188</v>
+      </c>
+      <c r="E34" s="9">
+        <v>46190</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="11">
+        <v>46190</v>
       </c>
     </row>
   </sheetData>
@@ -903,16 +1066,25 @@
     <hyperlink ref="C21" r:id="rId14" xr:uid="{0D45F11B-0B59-4324-9440-1F17A399A200}"/>
     <hyperlink ref="C22" r:id="rId15" xr:uid="{0EBFF9D6-79AC-46F5-92BE-47D794698BA9}"/>
     <hyperlink ref="C23" r:id="rId16" xr:uid="{CCB8B81B-A89E-4EAD-96D4-BE051752FE06}"/>
+    <hyperlink ref="C25" r:id="rId17" xr:uid="{395A4E3C-0FC7-4AF7-AFE5-9DA8C2EF4C2D}"/>
+    <hyperlink ref="C26" r:id="rId18" xr:uid="{6E212619-956A-4EED-B1D9-AE87A0F63C89}"/>
+    <hyperlink ref="C27" r:id="rId19" xr:uid="{A543C7D3-EC14-490B-95BE-FC3F4264FE4E}"/>
+    <hyperlink ref="C28" r:id="rId20" xr:uid="{E81BA7CE-0B2B-47FB-B7DB-56EA01EB74BB}"/>
+    <hyperlink ref="C29" r:id="rId21" xr:uid="{96B1ADB1-4C4A-446D-A5D7-22222C47A8BD}"/>
+    <hyperlink ref="C31" r:id="rId22" xr:uid="{528686DC-E698-4373-A87A-309F94EA5E16}"/>
+    <hyperlink ref="C34" r:id="rId23" xr:uid="{4950B584-431A-496E-9731-DC45DA08C560}"/>
+    <hyperlink ref="C35" r:id="rId24" xr:uid="{FCA619A5-31DD-4310-8CC1-97A6F41D47FA}"/>
+    <hyperlink ref="C32" r:id="rId25" xr:uid="{4E848B66-3739-4B95-AF41-B99FC25A8A19}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId17"/>
+  <pageSetup orientation="portrait" r:id="rId26"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44D7C9BB-1316-48AD-8614-AE27840B57E1}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
   </cols>

--- a/Preparation.xlsx
+++ b/Preparation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sghos\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B2F9EF-816A-4784-84E9-85965A74B237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83FAEA5C-89F2-4710-B0F2-8EDAA97D1B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>Day 1: Arrays &amp; Strings</t>
   </si>
@@ -202,12 +203,30 @@
   <si>
     <t xml:space="preserve">             </t>
   </si>
+  <si>
+    <t>Day 8:Hash Tables &amp; Hashing</t>
+  </si>
+  <si>
+    <t>Group Anagram</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/group-anagrams/</t>
+  </si>
+  <si>
+    <t>Day 9: Heaps &amp; Priority Queues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kth Largest Element in Array </t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/kth-largest-element-in-an-array/submissions/2039449974/</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -264,6 +283,11 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -298,7 +322,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -331,6 +355,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -613,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:J35"/>
+  <dimension ref="A2:K39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.85546875" style="6" customWidth="1"/>
@@ -626,15 +653,16 @@
     <col min="8" max="8" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20.28515625" customWidth="1"/>
     <col min="10" max="10" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="14"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
@@ -660,7 +688,7 @@
         <v>46183</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C4" s="2" t="s">
         <v>3</v>
       </c>
@@ -671,7 +699,7 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
@@ -690,8 +718,9 @@
       <c r="H5" s="4">
         <v>46176</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I5" s="9"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C6" s="2" t="s">
         <v>6</v>
       </c>
@@ -707,8 +736,11 @@
       <c r="G6" s="4">
         <v>46183</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="H6" s="9">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
         <v>7</v>
       </c>
@@ -722,13 +754,13 @@
         <v>46116</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="14"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
         <v>10</v>
       </c>
@@ -757,7 +789,7 @@
         <v>46180</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">
         <v>12</v>
       </c>
@@ -785,8 +817,11 @@
       <c r="J11" s="4">
         <v>46183</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="K11" s="9">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
         <v>14</v>
       </c>
@@ -815,13 +850,13 @@
         <v>46180</v>
       </c>
     </row>
-    <row r="14" spans="1:10" s="15" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>16</v>
       </c>
       <c r="B14" s="14"/>
     </row>
-    <row r="15" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
         <v>17</v>
       </c>
@@ -838,7 +873,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B16" s="12" t="s">
         <v>19</v>
       </c>
@@ -850,6 +885,9 @@
       </c>
       <c r="E16" s="4">
         <v>46181</v>
+      </c>
+      <c r="F16" s="9">
+        <v>46192</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -890,6 +928,9 @@
       <c r="E20" s="4">
         <v>46183</v>
       </c>
+      <c r="F20" s="9">
+        <v>46192</v>
+      </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
@@ -904,6 +945,9 @@
       <c r="E21" s="4">
         <v>46183</v>
       </c>
+      <c r="F21" s="9">
+        <v>46192</v>
+      </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C22" s="2" t="s">
@@ -912,6 +956,9 @@
       <c r="D22" s="4">
         <v>46183</v>
       </c>
+      <c r="E22" s="9">
+        <v>46192</v>
+      </c>
     </row>
     <row r="23" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B23" s="17" t="s">
@@ -933,7 +980,7 @@
       </c>
       <c r="B24" s="14"/>
     </row>
-    <row r="25" spans="1:8" ht="33" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B25" s="18" t="s">
         <v>33</v>
       </c>
@@ -988,7 +1035,7 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="30" spans="1:8" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
         <v>41</v>
       </c>
@@ -1017,7 +1064,7 @@
       </c>
       <c r="D32" s="9"/>
     </row>
-    <row r="33" spans="1:5" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
         <v>46</v>
       </c>
@@ -1046,6 +1093,34 @@
       </c>
       <c r="D35" s="11">
         <v>46190</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" s="15" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A36" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" s="14"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B37" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" s="14"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B39" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1075,9 +1150,11 @@
     <hyperlink ref="C34" r:id="rId23" xr:uid="{4950B584-431A-496E-9731-DC45DA08C560}"/>
     <hyperlink ref="C35" r:id="rId24" xr:uid="{FCA619A5-31DD-4310-8CC1-97A6F41D47FA}"/>
     <hyperlink ref="C32" r:id="rId25" xr:uid="{4E848B66-3739-4B95-AF41-B99FC25A8A19}"/>
+    <hyperlink ref="C37" r:id="rId26" xr:uid="{62632626-5569-42C5-9B39-4A59D03DE2BE}"/>
+    <hyperlink ref="C39" r:id="rId27" xr:uid="{DF1B008C-693A-4396-8D60-7F3DD8E9FABA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId26"/>
+  <pageSetup orientation="portrait" r:id="rId28"/>
 </worksheet>
 </file>
 
